--- a/tasks/forms/app/trigger_report_task.xlsx
+++ b/tasks/forms/app/trigger_report_task.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="5"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="survey" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="settings" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="chtx" state="veryHidden" r:id="rId6"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="settings" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="chtx" sheetId="3" state="hidden" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Author</author>
   </authors>
@@ -24,89 +30,349 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Determines what kinds of values are allowed and how the field is displayed. For certain types, further customization is possible using the appearance and parameters columns.
 https://docs.getodk.org/form-question-types/</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>Variable name. It may not contain spaces and must start with a letter or underscore. You should use a short, descriptive name and can use underscores to separate words. For example: date_of_birth.</t>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Variable name. It may not contain spaces and must start with a letter or underscore. You should use a short, descriptive name and can use underscores to separate words. For example: date_of_birth.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">The user-visible question text for the field. For example: "When was ${first_name} born?" This text can optionally reference other fields or be styled using subsets of Markdown and HTML.
 Can be translated.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">A hint that will be shown to the user below the question's label in smaller text.
 Can be translated.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Leave blank for questions that aren't required. Write yes for questions that are required. You can also use an expression to make a question conditionally required.
 https://docs.getodk.org/form-logic/#requiring-responses</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">An expression that determines whether a question will be displayed to a user or not. Lets you define branching or skip logic. 
 See the Relevance tab for examples.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">One or more modifiers that determine how the question will be displayed.
 These can be specific to the field type.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">A fixed value or an expression that will be evaluated once on form load. The value can then be modified by the user.
 https://docs.getodk.org/form-logic/#setting-default-responses</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="I1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">An expression that will be evaluated to determine the value of the field.
 Expressions may be re-evaluated at any time. Question types with calculations should be marked as read-only. Otherwise, a user-provided value may be replaced by a calculated one.
 To limit when expressions are evaluated, for example to specify dynamic defaults, use the trigger column or the once() function. 
 https://docs.getodk.org/form-logic/#when-expressions-are-evaluated</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J1" authorId="0">
       <text>
         <r>
-          <t>Can include a human-friendly note to describe the row. This will be ignored by all ODK tools.</t>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Can include a human-friendly note to describe the row. This will be ignored by all ODK tools.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Author</author>
   </authors>
@@ -114,36 +380,140 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">The title that will be displayed to anyone who uses this form.
 https://docs.getodk.org/xlsform/#the-settings-sheet</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">The unique version code that identifies the current state of the form. A common convention is to use a format like yyyymmddrr. For example, 2017021501 is the 1st revision from Feb 15th, 2017.
 A formula can be used to update the version automatically: `=TEXT(NOW(), "yyyymmddhhmmss")`
 This `version` is recorded in the form xml and is primarily useful for determining which version of the xlsform was used to produce the xml. A separate `form_version` property is generated for each form when it is uploaded to the CHT server. This is the version set on report docs produced by the form.
 https://docs.communityhealthtoolkit.org/building/forms/versioning/</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Specify different ways of displaying questions. 
 pages: show each question or field list on its own page.
 By default, all questions are shown on a single page.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t>Specify the custom namespaces used in the form. For example: `cht=https://communityhealthtoolkit.org`.</t>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Specify the custom namespaces used in the form. For example: `cht=https://communityhealthtoolkit.org`.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
@@ -152,201 +522,227 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
   <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label::English (en)</t>
-  </si>
-  <si>
-    <t>hint::English (en)</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>begin_group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
-    <t>./source = 'user'</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>contact</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>_id</t>
-  </si>
-  <si>
-    <t>Which contact do you want to trigger a `report` task for?</t>
-  </si>
-  <si>
-    <t>true()</t>
-  </si>
-  <si>
-    <t>select-contact</t>
-  </si>
-  <si>
-    <t>end_group</t>
-  </si>
-  <si>
-    <t>calculate</t>
-  </si>
-  <si>
-    <t>patient_uuid</t>
-  </si>
-  <si>
-    <t>../inputs/contact/_id</t>
-  </si>
-  <si>
-    <t>submit</t>
-  </si>
-  <si>
-    <t>Are you sure you want to trigger a task?</t>
-  </si>
-  <si>
-    <t>Each time this form is submitted, it will trigger a new task for the associated contact.</t>
-  </si>
-  <si>
-    <t>form_title</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>namespaces</t>
-  </si>
-  <si>
-    <t>Trigger Report Task</t>
-  </si>
-  <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>cht=https://communityhealthtoolkit.org</t>
-  </si>
-  <si>
-    <t>survey_header_names</t>
-  </si>
-  <si>
-    <t>settings_header_names</t>
-  </si>
-  <si>
-    <t>allow_choice_duplicates</t>
-  </si>
-  <si>
-    <t>audio</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message</t>
-  </si>
-  <si>
-    <t>hint</t>
-  </si>
-  <si>
-    <t>image</t>
-  </si>
-  <si>
-    <t>instance::cht:duration</t>
-  </si>
-  <si>
-    <t>instance::cht:unique_tel</t>
-  </si>
-  <si>
-    <t>instance::db-doc</t>
-  </si>
-  <si>
-    <t>instance::db-doc-ref</t>
-  </si>
-  <si>
-    <t>instance::tag</t>
-  </si>
-  <si>
-    <t>instance::type</t>
-  </si>
-  <si>
-    <t>label</t>
-  </si>
-  <si>
-    <t>parameters</t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
-    <t>required_message</t>
-  </si>
-  <si>
-    <t>trigger</t>
-  </si>
-  <si>
-    <t>video</t>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relevant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">appearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">begin_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./source = 'user'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which contact do you want to trigger a `report` task for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">select-contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patient_uuid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/contact/_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are you sure you want to trigger a task?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each time this form is submitted, it will trigger a new task for the associated contact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">form_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">namespaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger Report Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cht=https://communityhealthtoolkit.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">survey_header_names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settings_header_names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allow_choice_duplicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">audio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice_filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint_message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::cht:duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::cht:unique_tel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::db-doc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::db-doc-ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">read_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repeat_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required_message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+  </numFmts>
+  <fonts count="6">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Liberation Sans"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -358,7 +754,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -366,49 +762,87 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+  <cellXfs count="4">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <dxfs count="25">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
         <sz val="10"/>
-        <name val="Liberation Sans"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAFD095"/>
-        </patternFill>
-      </fill>
-      <border>
+        <patternFill>
+          <bgColor rgb="FFAFD095"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
         <left style="thin">
           <color rgb="FF808080"/>
         </left>
@@ -422,17 +856,19 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
         <sz val="10"/>
-        <name val="Liberation Sans"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD3D3D3"/>
-        </patternFill>
-      </fill>
-      <border>
+        <patternFill>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
         <left style="thin">
           <color rgb="FF808080"/>
         </left>
@@ -446,17 +882,19 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
         <sz val="10"/>
-        <name val="Liberation Sans"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCF0"/>
-        </patternFill>
-      </fill>
-      <border>
+        <patternFill>
+          <bgColor rgb="FFCCCCF0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
         <left style="thin">
           <color rgb="FF808080"/>
         </left>
@@ -470,16 +908,18 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
         <sz val="10"/>
-        <name val="Liberation Sans"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAFD095"/>
-        </patternFill>
-      </fill>
-      <border>
+        <patternFill>
+          <bgColor rgb="FFAFD095"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
         <left style="thin">
           <color rgb="FF808080"/>
         </left>
@@ -493,16 +933,18 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
         <sz val="10"/>
-        <name val="Liberation Sans"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD3D3D3"/>
-        </patternFill>
-      </fill>
-      <border>
+        <patternFill>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
         <left style="thin">
           <color rgb="FF808080"/>
         </left>
@@ -516,16 +958,18 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
         <sz val="10"/>
-        <name val="Liberation Sans"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCF0"/>
-        </patternFill>
-      </fill>
-      <border>
+        <patternFill>
+          <bgColor rgb="FFCCCCF0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
         <left style="thin">
           <color rgb="FF808080"/>
         </left>
@@ -539,48 +983,48 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <border>
+      <border diagonalUp="false" diagonalDown="false">
         <left/>
         <right/>
         <top style="medium">
@@ -591,7 +1035,7 @@
       </border>
     </dxf>
     <dxf>
-      <border>
+      <border diagonalUp="false" diagonalDown="false">
         <left/>
         <right/>
         <top/>
@@ -602,7 +1046,7 @@
       </border>
     </dxf>
     <dxf>
-      <border>
+      <border diagonalUp="false" diagonalDown="false">
         <left/>
         <right/>
         <top style="medium">
@@ -613,7 +1057,7 @@
       </border>
     </dxf>
     <dxf>
-      <border>
+      <border diagonalUp="false" diagonalDown="false">
         <left/>
         <right/>
         <top/>
@@ -625,38 +1069,40 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
         <sz val="10"/>
-        <name val="Liberation Sans"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD3D3D3"/>
-        </patternFill>
-      </fill>
-      <border>
+        <patternFill>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
         <left style="thin">
           <color rgb="FF808080"/>
         </left>
@@ -670,16 +1116,18 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
         <sz val="10"/>
-        <name val="Liberation Sans"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD3D3D3"/>
-        </patternFill>
-      </fill>
-      <border>
+        <patternFill>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
         <left style="thin">
           <color rgb="FF808080"/>
         </left>
@@ -693,28 +1141,79 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFD3D3D3"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF7030A0"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0070C0"/>
+      <rgbColor rgb="FFCCCCF0"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -726,37 +1225,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -825,45 +1324,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="12.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.53515625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="11.53" style="1" customWidth="1"/>
-    <col min="3" max="3" width="46.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.66" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.48" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.37" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.09" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.8" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.57" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.53" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="9" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="9" style="1" customWidth="1"/>
-    <col min="26" max="16384" width="11.53" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.57"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="11" style="1" width="9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="26" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -888,21 +1376,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="12.8" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="12.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -912,9 +1397,6 @@
       <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
         <v>16</v>
       </c>
@@ -922,7 +1404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="12.8" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -933,7 +1415,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="12.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -943,16 +1425,14 @@
       <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -960,7 +1440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -968,24 +1448,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="12.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" ht="12.8" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -999,116 +1473,98 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" ht="12.8" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" ht="12.8" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" ht="12.8" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:BI1">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BI$1,A1)&gt;1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(A1&lt;&gt;"",NOT(OR(A1="audio",LEFT(A1,7)="audio::",A1="constraint_message",LEFT(A1,20)="constraint_message::",A1="hint",LEFT(A1,6)="hint::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="required_message",LEFT(A1,18)="required_message::",A1="video",LEFT(A1,7)="video::")),NOT(NOT(ISERROR(MATCH(A1,{"appearance","instance::cht:duration","instance::cht:unique_tel","instance::db-doc","instance::db-doc-ref","instance::tag","instance::type","name","note","parameters","read_only","trigger","type"},0)))),NOT(NOT(ISERROR(MATCH(A1,{"calculation","choice_filter","constraint","default","relevant","repeat_count","required"},0)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(OR(A1="audio",LEFT(A1,7)="audio::",A1="constraint_message",LEFT(A1,20)="constraint_message::",A1="hint",LEFT(A1,6)="hint::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="required_message",LEFT(A1,18)="required_message::",A1="video",LEFT(A1,7)="video::"),COUNTA(A$2:A$1015)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(NOT(ISERROR(MATCH(A1,{"appearance","instance::cht:duration","instance::cht:unique_tel","instance::db-doc","instance::db-doc-ref","instance::tag","instance::type","name","note","parameters","read_only","trigger","type"},0))),COUNTA(A$2:A$1015)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>AND(NOT(ISERROR(MATCH(A1,{"calculation","choice_filter","constraint","default","relevant","repeat_count","required"},0))),COUNTA(A$2:A$1015)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>OR(A1="audio",LEFT(A1,7)="audio::",A1="constraint_message",LEFT(A1,20)="constraint_message::",A1="hint",LEFT(A1,6)="hint::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="required_message",LEFT(A1,18)="required_message::",A1="video",LEFT(A1,7)="video::")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>NOT(ISERROR(MATCH(A1,{"appearance","instance::cht:duration","instance::cht:unique_tel","instance::db-doc","instance::db-doc-ref","instance::tag","instance::type","name","note","parameters","read_only","trigger","type"},0)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>NOT(ISERROR(MATCH(A1,{"calculation","choice_filter","constraint","default","relevant","repeat_count","required"},0)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A1015">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>AND(A2&lt;&gt;"",NOT(OR(NOT(ISERROR(MATCH(A2,{"acknowledge","audio","begin_group","begin_repeat","calculate","date","datetime","decimal","end","end_group","end_repeat","file","geopoint","geoshape","geotrace","hidden","image","integer","note","range","rank","start","text","time","today","video"},0))),FALSE,FALSE)))</formula>
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>AND(A2&lt;&gt;"",NOT(OR(NOT(ISERROR(MATCH(A2,{"acknowledge","audio","begin_group","begin_repeat","calculate","date","datetime","decimal","end","end_group","end_repeat","file","geopoint","geoshape","geotrace","hidden","image","integer","note","range","rank","start","text","time","today","video"},0))),0,0)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B1015">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>AND(A2&lt;&gt;"",B2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C1015">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>AND(OR(NOT(ISERROR(MATCH(A2,{"acknowledge","audio","date","datetime","decimal","file","geopoint","geoshape","geotrace","image","integer","note","range","rank","text","time","video"},0))),LEFT(A2,11)="select_one ",LEFT(A2,16)="select_multiple "),C2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>AND(C2&lt;&gt;"",NOT(ISERROR(MATCH(A2,{"calculate","end","end_group","end_repeat","hidden","start","today"},0))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>OR(C2="NO_LABEL",C2="DELETE_THIS_LINE")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I1015">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>AND(A2="calculate",I2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:BI1015">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>AND($A2="begin_group",A$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:BI1015">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>AND($A2="end_group",A$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:BI1015">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>AND($A2="begin_repeat",A$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:BI1015">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>AND($A2="end_repeat",A$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:BI1015">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>AND(A2&lt;&gt;"",A$1="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="information" errorTitle="Column warning" error="For translatable columns, you can append &quot;::&lt;lang&gt;&quot; to the column name (e.g., label::en)." sqref="A1:BI1">
-      <formula1>'chtx'!$A$2:$A$28</formula1>
+    <dataValidation allowBlank="true" error="For translatable columns, you can append &quot;::&lt;lang&gt;&quot; to the column name (e.g., label::en)." errorStyle="information" errorTitle="Column warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:BI1" type="list">
+      <formula1>chtx!$A$2:$A$28</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="information" errorTitle="Type warning" error="If configuring a select, ensure your list name matches a list from the choices sheet." sqref="A2:A1015">
+    <dataValidation allowBlank="true" error="If configuring a select, ensure your list name matches a list from the choices sheet." errorStyle="information" errorTitle="Type warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A1012" type="list">
       <formula1>"acknowledge,audio,begin_group,begin_repeat,calculate,date,datetime,decimal,end,end_group,end_repeat,file,geopoint,geoshape,geotrace,hidden,image,integer,note,range,rank,select_multiple list_name,select_one list_name,start,text,time,today,video"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
@@ -1117,39 +1573,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="12.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.53515625" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.99" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.89" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.61" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.61"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" ht="12.8" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f>TEXT(NOW(), "yyyymmddhhmmss")</f>
-        <v>20260722213232</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <f aca="true">TEXT(NOW(), "yyyymmddhhmmss")</f>
+        <v>20260722164459</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1158,40 +1617,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:BC1">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BC$1,A1)&gt;1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>AND(A1&lt;&gt;"",NOT(NOT(ISERROR(MATCH(A1,{"allow_choice_duplicates","form_title","namespaces","style","version"},0)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="3">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>AND(A1&lt;&gt;"",COUNTA(A$2:A$1002)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="4">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>NOT(ISERROR(MATCH(A1,{"allow_choice_duplicates","form_title","namespaces","style","version"},0)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C1002">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>AND(C2&lt;&gt;"",C2&lt;&gt;"pages")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:BC1002">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>AND(A2&lt;&gt;"",A$1="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="information" errorTitle="Column warning" error="Unexpected column name." sqref="A1:BC1">
-      <formula1>'chtx'!$C$2:$C$6</formula1>
+    <dataValidation allowBlank="true" error="Unexpected column name." errorStyle="information" errorTitle="Column warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:BC1" type="list">
+      <formula1>chtx!$C$2:$C$6</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="This column only accepts &quot;pages&quot; or an empty value." sqref="C2:C1002">
+    <dataValidation allowBlank="true" error="This column only accepts &quot;pages&quot; or an empty value." errorStyle="stop" errorTitle="Invalid value" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C1002" type="list">
       <formula1>",pages"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
@@ -1200,170 +1662,178 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>59</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/tasks/forms/app/trigger_report_task.xlsx
+++ b/tasks/forms/app/trigger_report_task.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <fileVersion appName="Calc" lowestEdited="5"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -10,20 +10,21 @@
   <sheets>
     <sheet name="survey" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="settings" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="chtx" sheetId="3" state="hidden" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
-    <author>Unknown Author</author>
+    <author>Author</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -35,20 +36,30 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Determines what kinds of values are allowed and how the field is displayed. For certain types, further customization is possible using the appearance and parameters columns.
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF0000FF"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">https://docs.getodk.org/form-question-types/
-</t>
+https://docs.getodk.org/form-question-types/</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
@@ -61,6 +72,27 @@
           <t xml:space="preserve">Variable name. It may not contain spaces and must start with a letter or underscore. You should use a short, descriptive name and can use underscores to separate words. For example: date_of_birth.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
@@ -74,6 +106,27 @@
 Can be translated.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
@@ -87,6 +140,27 @@
 Can be translated.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
@@ -100,6 +174,27 @@
 https://docs.getodk.org/form-logic/#requiring-responses</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F1" authorId="0">
       <text>
@@ -110,9 +205,30 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">An expression that determines whether a question will be displayed to a user or not. Lets you define branching or skip logic. 
-https://docs.getodk.org/form-logic/#conditionally-showing-questions</t>
+See the Relevance tab for examples.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G1" authorId="0">
       <text>
@@ -126,6 +242,27 @@
 These can be specific to the field type.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H1" authorId="0">
       <text>
@@ -139,6 +276,27 @@
 https://docs.getodk.org/form-logic/#setting-default-responses</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="I1" authorId="0">
       <text>
@@ -149,11 +307,32 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">An expression that will be evaluated to determine the value of the field.
-⚠️ Expressions may be re-evaluated at any time. 
-To limit when expressions are evaluated, for example to specify dynamic defaults use the once() function. 
+Expressions may be re-evaluated at any time. Question types with calculations should be marked as read-only. Otherwise, a user-provided value may be replaced by a calculated one.
+To limit when expressions are evaluated, for example to specify dynamic defaults, use the trigger column or the once() function. 
 https://docs.getodk.org/form-logic/#when-expressions-are-evaluated</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J1" authorId="0">
       <text>
@@ -166,15 +345,36 @@
           <t xml:space="preserve">Can include a human-friendly note to describe the row. This will be ignored by all ODK tools.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
-    <author>Unknown Author</author>
+    <author>Author</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -189,6 +389,27 @@
 https://docs.getodk.org/xlsform/#the-settings-sheet</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
@@ -199,9 +420,32 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">The unique version code that identifies the current state of the form. A common convention is to use a format like yyyymmddrr. For example, 2017021501 is the 1st revision from Feb 15th, 2017.
-By default, this template uses a formula to create a date-based version that will update automatically.</t>
+A formula can be used to update the version automatically: `=TEXT(NOW(), "yyyymmddhhmmss")`
+This `version` is recorded in the form xml and is primarily useful for determining which version of the xlsform was used to produce the xml. A separate `form_version` property is generated for each form when it is uploaded to the CHT server. This is the version set on report docs produced by the form.
+https://docs.communityhealthtoolkit.org/building/forms/versioning/</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
@@ -211,9 +455,32 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Set to ‘pages’ to indicate that groups with the `field-list` appearance represent separate form pages (and all other questions will be shown on their own page). </t>
+          <t xml:space="preserve">Specify different ways of displaying questions. 
+pages: show each question or field list on its own page.
+By default, all questions are shown on a single page.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
@@ -223,16 +490,37 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Custom namespaces supported in the form.  `cht` must be included here to use the custom `instance::cht` columns on the survey sheet.</t>
+          <t xml:space="preserve">Specify the custom namespaces used in the form. For example: `cht=https://communityhealthtoolkit.org`.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>2</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -240,10 +528,10 @@
     <t xml:space="preserve">name</t>
   </si>
   <si>
-    <t xml:space="preserve">label::English (en)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hint::English (en)</t>
+    <t xml:space="preserve">label::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint::en</t>
   </si>
   <si>
     <t xml:space="preserve">required</t>
@@ -346,21 +634,87 @@
   </si>
   <si>
     <t xml:space="preserve">cht=https://communityhealthtoolkit.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">survey_header_names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settings_header_names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allow_choice_duplicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">audio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice_filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint_message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::cht:duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::cht:unique_tel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::db-doc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::db-doc-ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">read_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repeat_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required_message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yy\ hh:mm\ AM/PM"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -380,10 +734,9 @@
       <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -391,35 +744,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FFCCCCCC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -427,71 +761,8 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF999999"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF3465A4"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF999999"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF3465A4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF5B277D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF999999"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF5B277D"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="26">
+  <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -515,88 +786,249 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="22" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="column_head" xfId="20"/>
-    <cellStyle name="column_head_i18n" xfId="21"/>
-    <cellStyle name="group_begin" xfId="22"/>
-    <cellStyle name="group_end" xfId="23"/>
-    <cellStyle name="repeat_begin" xfId="24"/>
-    <cellStyle name="repeat_end" xfId="25"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
+  <dxfs count="25">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAFD095"/>
+        </patternFill>
+      </fill>
       <border diagonalUp="false" diagonalDown="false">
-        <left style="hair">
-          <color rgb="FF999999"/>
+        <left style="thin">
+          <color rgb="FF808080"/>
         </left>
-        <right style="hair">
-          <color rgb="FF999999"/>
+        <right style="thin">
+          <color rgb="FF808080"/>
         </right>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="thin">
+          <color rgb="FF808080"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF808080"/>
+        </right>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCCCF0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="thin">
+          <color rgb="FF808080"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF808080"/>
+        </right>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAFD095"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="thin">
+          <color rgb="FF808080"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF808080"/>
+        </right>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="thin">
+          <color rgb="FF808080"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF808080"/>
+        </right>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCCCF0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="thin">
+          <color rgb="FF808080"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF808080"/>
+        </right>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
         <top style="medium">
-          <color rgb="FF3465A4"/>
+          <color rgb="FF0070C0"/>
         </top>
         <bottom/>
         <diagonal/>
@@ -604,29 +1036,21 @@
     </dxf>
     <dxf>
       <border diagonalUp="false" diagonalDown="false">
-        <left style="hair">
-          <color rgb="FF999999"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF999999"/>
-        </right>
+        <left/>
+        <right/>
         <top/>
         <bottom style="medium">
-          <color rgb="FF3465A4"/>
+          <color rgb="FF0070C0"/>
         </bottom>
         <diagonal/>
       </border>
     </dxf>
     <dxf>
       <border diagonalUp="false" diagonalDown="false">
-        <left style="hair">
-          <color rgb="FF999999"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF999999"/>
-        </right>
+        <left/>
+        <right/>
         <top style="medium">
-          <color rgb="FF5B277D"/>
+          <color rgb="FF7030A0"/>
         </top>
         <bottom/>
         <diagonal/>
@@ -634,26 +1058,98 @@
     </dxf>
     <dxf>
       <border diagonalUp="false" diagonalDown="false">
-        <left style="hair">
-          <color rgb="FF999999"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF999999"/>
-        </right>
+        <left/>
+        <right/>
         <top/>
         <bottom style="medium">
-          <color rgb="FF5B277D"/>
+          <color rgb="FF7030A0"/>
         </bottom>
         <diagonal/>
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
-        <color rgb="FFCC0000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
+        <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="thin">
+          <color rgb="FF808080"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF808080"/>
+        </right>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="thin">
+          <color rgb="FF808080"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF808080"/>
+        </right>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -662,7 +1158,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -674,16 +1170,16 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FFD3D3D3"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF7030A0"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF0070C0"/>
+      <rgbColor rgb="FFCCCCF0"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -699,22 +1195,22 @@
       <rgbColor rgb="FFAFD095"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCCCC"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF3465A4"/>
-      <rgbColor rgb="FF999999"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF5B277D"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -729,37 +1225,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -832,8 +1328,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.5"/>
@@ -844,43 +1340,44 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="11" style="1" width="9"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="26" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -890,8 +1387,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -907,8 +1404,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -918,8 +1415,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -935,24 +1432,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -962,7 +1459,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,59 +1473,91 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="5"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A16:J9999 A13:D15 F13:J15 A2:J12">
+  <conditionalFormatting sqref="A1:BI1">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$A2="begin_group"</formula>
+      <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BI$1,A1)&gt;1)</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>$A2="end_group"</formula>
+      <formula>AND(A1&lt;&gt;"",NOT(OR(A1="audio",LEFT(A1,7)="audio::",A1="constraint_message",LEFT(A1,20)="constraint_message::",A1="hint",LEFT(A1,6)="hint::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="required_message",LEFT(A1,18)="required_message::",A1="video",LEFT(A1,7)="video::")),NOT(NOT(ISERROR(MATCH(A1,{"appearance","instance::cht:duration","instance::cht:unique_tel","instance::db-doc","instance::db-doc-ref","instance::tag","instance::type","name","note","parameters","read_only","trigger","type"},0)))),NOT(NOT(ISERROR(MATCH(A1,{"calculation","choice_filter","constraint","default","relevant","repeat_count","required"},0)))))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>$A2="begin_repeat"</formula>
+      <formula>AND(OR(A1="audio",LEFT(A1,7)="audio::",A1="constraint_message",LEFT(A1,20)="constraint_message::",A1="hint",LEFT(A1,6)="hint::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="required_message",LEFT(A1,18)="required_message::",A1="video",LEFT(A1,7)="video::"),COUNTA(A$2:A$1015)=0)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>$A2="end_repeat"</formula>
+      <formula>AND(NOT(ISERROR(MATCH(A1,{"appearance","instance::cht:duration","instance::cht:unique_tel","instance::db-doc","instance::db-doc-ref","instance::tag","instance::type","name","note","parameters","read_only","trigger","type"},0))),COUNTA(A$2:A$1015)=0)</formula>
     </cfRule>
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>AND(ISBLANK($A2), NOT(ISBLANK(A2)))</formula>
+      <formula>AND(NOT(ISERROR(MATCH(A1,{"calculation","choice_filter","constraint","default","relevant","repeat_count","required"},0))),COUNTA(A$2:A$1015)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>OR(A1="audio",LEFT(A1,7)="audio::",A1="constraint_message",LEFT(A1,20)="constraint_message::",A1="hint",LEFT(A1,6)="hint::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="required_message",LEFT(A1,18)="required_message::",A1="video",LEFT(A1,7)="video::")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>NOT(ISERROR(MATCH(A1,{"appearance","instance::cht:duration","instance::cht:unique_tel","instance::db-doc","instance::db-doc-ref","instance::tag","instance::type","name","note","parameters","read_only","trigger","type"},0)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>NOT(ISERROR(MATCH(A1,{"calculation","choice_filter","constraint","default","relevant","repeat_count","required"},0)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9999">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>AND(ISBLANK(B2), NOT(ISBLANK($A2)))</formula>
+  <conditionalFormatting sqref="A2:A1015">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>AND(A2&lt;&gt;"",NOT(OR(NOT(ISERROR(MATCH(A2,{"acknowledge","audio","begin_group","begin_repeat","calculate","date","datetime","decimal","end","end_group","end_repeat","file","geopoint","geoshape","geotrace","hidden","image","integer","note","range","rank","start","text","time","today","video"},0))),0,0)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9999">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>AND(ISBLANK(C2),NOT(OR(ISBLANK($A2),$A2="calculate")))</formula>
+  <conditionalFormatting sqref="B2:B1015">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>AND(A2&lt;&gt;"",B2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9999">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>AND($A2="calculate", ISBLANK(I2))</formula>
+  <conditionalFormatting sqref="C2:C1015">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>AND(OR(NOT(ISERROR(MATCH(A2,{"acknowledge","audio","date","datetime","decimal","file","geopoint","geoshape","geotrace","image","integer","note","range","rank","text","time","video"},0))),LEFT(A2,11)="select_one ",LEFT(A2,16)="select_multiple "),C2="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>AND(C2&lt;&gt;"",NOT(ISERROR(MATCH(A2,{"calculate","end","end_group","end_repeat","hidden","start","today"},0))))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>OR(C2="NO_LABEL",C2="DELETE_THIS_LINE")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" error="If configuring a select, ensure your list name matches a list from the choices sheet." errorStyle="information" operator="equal" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A1" type="none">
-      <formula1>0</formula1>
+  <conditionalFormatting sqref="I2:I1015">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>AND(A2="calculate",I2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:BI1015">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>AND($A2="begin_group",A$1&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:BI1015">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>AND($A2="end_group",A$1&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:BI1015">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+      <formula>AND($A2="begin_repeat",A$1&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:BI1015">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>AND($A2="end_repeat",A$1&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:BI1015">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>AND(A2&lt;&gt;"",A$1="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="For translatable columns, you can append &quot;::&lt;lang&gt;&quot; to the column name (e.g., label::en)." errorStyle="information" errorTitle="Column warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:BI1" type="list">
+      <formula1>chtx!$A$2:$A$28</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="If configuring a select, ensure your list name matches a list from the choices sheet." errorStyle="information" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2 A9 A11:A1014" type="list">
-      <formula1>"begin_group,end_group,note,calculate,text,integer,decimal,select_one list_name,select_multiple list_name,date,time,datetime,begin_repeat,end_repeat,geopoint,geotrace,geoshape,start-geopoint,range,image,audio,video,file,rank,acknowledge,start,end,today"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="If configuring a select, ensure your list name matches a list from the choices sheet." errorStyle="information" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A3:A8 A10" type="list">
-      <formula1>"begin_group,end_group,note,calculate,text,integer,decimal,select_one list_name,select_multiple list_name,date,time,datetime,begin_repeat,end_repeat,geopoint,geotrace,geoshape,start-geopoint,range,image,audio,video,file,rank,acknowledge,start,end,today"</formula1>
+    <dataValidation allowBlank="true" error="If configuring a select, ensure your list name matches a list from the choices sheet." errorStyle="information" errorTitle="Type warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A1012" type="list">
+      <formula1>"acknowledge,audio,begin_group,begin_repeat,calculate,date,datetime,decimal,end,end_group,end_repeat,file,geopoint,geoshape,geotrace,hidden,image,integer,note,range,rank,select_multiple list_name,select_one list_name,start,text,time,today,video"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1049,50 +1578,262 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="17.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="16.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="32.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.61"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="1" t="str">
         <f aca="true">TEXT(NOW(), "yyyymmddhhmmss")</f>
-        <v>20260114093045</v>
-      </c>
-      <c r="C2" s="5" t="s">
+        <v>20260722164459</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:BC1">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+      <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BC$1,A1)&gt;1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+      <formula>AND(A1&lt;&gt;"",NOT(NOT(ISERROR(MATCH(A1,{"allow_choice_duplicates","form_title","namespaces","style","version"},0)))))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+      <formula>AND(A1&lt;&gt;"",COUNTA(A$2:A$1002)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+      <formula>NOT(ISERROR(MATCH(A1,{"allow_choice_duplicates","form_title","namespaces","style","version"},0)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C1002">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+      <formula>AND(C2&lt;&gt;"",C2&lt;&gt;"pages")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:BC1002">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+      <formula>AND(A2&lt;&gt;"",A$1="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Unexpected column name." errorStyle="information" errorTitle="Column warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:BC1" type="list">
+      <formula1>chtx!$C$2:$C$6</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="This column only accepts &quot;pages&quot; or an empty value." errorStyle="stop" errorTitle="Invalid value" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C1002" type="list">
+      <formula1>",pages"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>